--- a/Cambio parametro FAN.xlsx
+++ b/Cambio parametro FAN.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EFCA98E-DE7E-46BD-8ADE-15F4D035CA37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D039F8-1AB0-4237-9756-3BB8E8045B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D5E8A3BA-DF38-449C-B3FD-346E467AFD01}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="96">
   <si>
     <t>13_482</t>
   </si>
@@ -238,13 +239,100 @@
   </si>
   <si>
     <t>13_242</t>
+  </si>
+  <si>
+    <t>02_408</t>
+  </si>
+  <si>
+    <t>reset exitoso</t>
+  </si>
+  <si>
+    <t>10_014</t>
+  </si>
+  <si>
+    <t>08_073</t>
+  </si>
+  <si>
+    <t>05_855</t>
+  </si>
+  <si>
+    <t>04_509</t>
+  </si>
+  <si>
+    <t>revisar despues  de contingencia</t>
+  </si>
+  <si>
+    <t>13_790</t>
+  </si>
+  <si>
+    <t>04_324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_363 </t>
+  </si>
+  <si>
+    <t>04_007</t>
+  </si>
+  <si>
+    <t>escalado  a noc</t>
+  </si>
+  <si>
+    <t>cambio g3b</t>
+  </si>
+  <si>
+    <t>04_452</t>
+  </si>
+  <si>
+    <t>oos</t>
+  </si>
+  <si>
+    <t>05_203</t>
+  </si>
+  <si>
+    <t>13_674</t>
+  </si>
+  <si>
+    <t>problemas  de acceso</t>
+  </si>
+  <si>
+    <t>victor</t>
+  </si>
+  <si>
+    <t>ugaz</t>
+  </si>
+  <si>
+    <t>roberto</t>
+  </si>
+  <si>
+    <t>yo</t>
+  </si>
+  <si>
+    <t>edison</t>
+  </si>
+  <si>
+    <t>marco</t>
+  </si>
+  <si>
+    <t>andres</t>
+  </si>
+  <si>
+    <t>oscar</t>
+  </si>
+  <si>
+    <t>04_342</t>
+  </si>
+  <si>
+    <t>cristian</t>
+  </si>
+  <si>
+    <t>08_819</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,8 +340,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -263,6 +362,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -276,10 +381,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -295,9 +401,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{B8D0763A-7BC7-435C-9B5F-F7AC9C9EEF42}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -609,20 +718,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6E13495-377A-4565-B031-AC975D82256A}">
-  <dimension ref="A2:F57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:H80"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.42578125" style="1"/>
     <col min="3" max="3" width="29.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3">
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -630,7 +739,7 @@
         <v>45388</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3">
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
@@ -638,7 +747,7 @@
         <v>45388</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3">
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
@@ -646,7 +755,7 @@
         <v>45389</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:3">
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
@@ -654,7 +763,7 @@
         <v>45389</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3">
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
@@ -662,7 +771,7 @@
         <v>45390</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:3">
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
@@ -670,7 +779,7 @@
         <v>45390</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:3">
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
@@ -678,7 +787,7 @@
         <v>45391</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:3">
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
@@ -686,7 +795,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:3">
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
@@ -694,7 +803,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:3">
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
@@ -702,7 +811,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:3">
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
@@ -710,7 +819,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:3">
       <c r="B14" s="1" t="s">
         <v>16</v>
       </c>
@@ -718,7 +827,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:3">
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
@@ -726,7 +835,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:3">
       <c r="B16" s="1" t="s">
         <v>12</v>
       </c>
@@ -734,7 +843,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
         <v>18</v>
       </c>
@@ -742,7 +851,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18" s="6"/>
       <c r="B18" s="1" t="s">
         <v>10</v>
@@ -751,7 +860,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="B19" s="1" t="s">
         <v>20</v>
       </c>
@@ -759,7 +868,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="B20" s="1" t="s">
         <v>21</v>
       </c>
@@ -767,7 +876,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="B21" s="1" t="s">
         <v>22</v>
       </c>
@@ -775,7 +884,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="B22" s="1" t="s">
         <v>23</v>
       </c>
@@ -783,7 +892,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="B23" s="1" t="s">
         <v>25</v>
       </c>
@@ -794,7 +903,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="B24" s="1" t="s">
         <v>27</v>
       </c>
@@ -802,7 +911,7 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="B25" s="1" t="s">
         <v>28</v>
       </c>
@@ -810,7 +919,7 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="B26" s="1" t="s">
         <v>29</v>
       </c>
@@ -818,7 +927,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="B27" s="1" t="s">
         <v>30</v>
       </c>
@@ -826,7 +935,7 @@
         <v>46148</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="B28" s="5" t="s">
         <v>31</v>
       </c>
@@ -834,7 +943,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
@@ -842,7 +951,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="B30" s="5" t="s">
         <v>2</v>
       </c>
@@ -850,7 +959,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="B31" s="1" t="s">
         <v>34</v>
       </c>
@@ -861,7 +970,7 @@
         <v>46153</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32" s="6"/>
       <c r="B32" s="1" t="s">
         <v>35</v>
@@ -873,7 +982,7 @@
         <v>46153</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33" s="6"/>
       <c r="B33" s="1" t="s">
         <v>37</v>
@@ -885,7 +994,7 @@
         <v>46153</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34" s="6"/>
       <c r="B34" s="1" t="s">
         <v>38</v>
@@ -897,7 +1006,7 @@
         <v>46153</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35" s="6"/>
       <c r="B35" s="1" t="s">
         <v>39</v>
@@ -909,7 +1018,7 @@
         <v>46153</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="B36" s="1" t="s">
         <v>2</v>
       </c>
@@ -920,7 +1029,7 @@
         <v>46153</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37" s="6"/>
       <c r="B37" s="1" t="s">
         <v>40</v>
@@ -932,7 +1041,7 @@
         <v>46154</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38" s="6"/>
       <c r="B38" s="1" t="s">
         <v>42</v>
@@ -944,7 +1053,7 @@
         <v>46154</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5">
       <c r="A39" s="6"/>
       <c r="B39" s="1" t="s">
         <v>44</v>
@@ -959,7 +1068,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="B42" s="1" t="s">
         <v>46</v>
       </c>
@@ -970,7 +1079,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5">
       <c r="B43" s="1" t="s">
         <v>47</v>
       </c>
@@ -981,7 +1090,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="B44" s="1" t="s">
         <v>48</v>
       </c>
@@ -990,7 +1099,7 @@
       </c>
       <c r="D44" s="1"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5">
       <c r="B45" s="1" t="s">
         <v>49</v>
       </c>
@@ -1001,7 +1110,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5">
       <c r="B46" s="1" t="s">
         <v>50</v>
       </c>
@@ -1012,7 +1121,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5">
       <c r="B47" s="1" t="s">
         <v>51</v>
       </c>
@@ -1023,7 +1132,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5">
       <c r="B48" s="1" t="s">
         <v>52</v>
       </c>
@@ -1034,7 +1143,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:4">
       <c r="B49" s="1" t="s">
         <v>53</v>
       </c>
@@ -1045,7 +1154,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:4">
       <c r="B50" s="1" t="s">
         <v>54</v>
       </c>
@@ -1053,7 +1162,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:4">
       <c r="B51" s="1" t="s">
         <v>55</v>
       </c>
@@ -1064,7 +1173,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:4">
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
@@ -1075,7 +1184,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:4">
       <c r="B53" s="1" t="s">
         <v>39</v>
       </c>
@@ -1083,7 +1192,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:4">
       <c r="B54" s="1" t="s">
         <v>62</v>
       </c>
@@ -1094,7 +1203,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:4">
       <c r="B55" s="1" t="s">
         <v>63</v>
       </c>
@@ -1103,7 +1212,7 @@
       </c>
       <c r="D55" s="1"/>
     </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:4">
       <c r="B56" s="1" t="s">
         <v>66</v>
       </c>
@@ -1112,11 +1221,243 @@
       </c>
       <c r="D56" s="1"/>
     </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:4">
+      <c r="B57" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="D57" s="1"/>
+    </row>
+    <row r="58" spans="2:4">
+      <c r="B58" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C58" s="1">
+        <v>5852050</v>
+      </c>
+      <c r="D58" s="1"/>
+    </row>
+    <row r="59" spans="2:4">
+      <c r="B59" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59" s="1">
+        <v>5852386</v>
+      </c>
+      <c r="D59" s="1"/>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="B60" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C60" s="1">
+        <v>5845852</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="B61" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D61" s="1"/>
+    </row>
+    <row r="62" spans="2:4">
+      <c r="D62" s="1"/>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="B64" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C64">
+        <v>5896120</v>
+      </c>
+      <c r="D64" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8">
+      <c r="B65" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8">
+      <c r="B67" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8">
+      <c r="B68" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8">
+      <c r="B69" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D69" t="s">
+        <v>79</v>
+      </c>
+      <c r="G69" t="s">
+        <v>80</v>
+      </c>
+      <c r="H69" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8">
+      <c r="G70" t="s">
+        <v>82</v>
+      </c>
+      <c r="H70" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" ht="15.75">
+      <c r="B72" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D72" s="8">
+        <v>5906090</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" ht="15.75">
+      <c r="B73" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D73" s="8"/>
+    </row>
+    <row r="74" spans="2:8">
+      <c r="B74" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8">
+      <c r="B77" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C77">
+        <v>5910282</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8">
+      <c r="C78"/>
+    </row>
+    <row r="79" spans="2:8">
+      <c r="B79" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C79">
+        <v>5899309</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8">
+      <c r="C80"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C38054C6-A97C-4CAA-99B0-02FA7E31CEFC}">
+  <dimension ref="C8:C20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="8" spans="3:3">
+      <c r="C8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3">
+      <c r="C14" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3">
+      <c r="C15" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>